--- a/outputs/daily/hr_rankings_2026-08-25_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25_full.xlsx
@@ -68523,27 +68523,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-08-25T22:40:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -68553,17 +68553,17 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Jackson Jobe</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -68572,7 +68572,7 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -68590,22 +68590,22 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="Q251" t="n">
-        <v>50.8</v>
+        <v>27.9</v>
       </c>
       <c r="R251" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S251" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T251" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U251" t="n">
-        <v>3.4</v>
+        <v>26.1</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -68644,7 +68644,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr"/>
@@ -68661,12 +68661,12 @@
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ251" t="inlineStr">
@@ -68676,12 +68676,12 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
@@ -68691,104 +68691,104 @@
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>85.88</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>95.4315</t>
+          <t>95.8533</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>0.2684</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>0.0745</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>0.2498</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>87.84</t>
         </is>
       </c>
       <c r="BD251" t="inlineStr">
         <is>
-          <t>0.4688</t>
+          <t>0.4084</t>
         </is>
       </c>
       <c r="BE251" t="inlineStr">
         <is>
-          <t>0.1988</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG251" t="inlineStr"/>
       <c r="BH251" t="inlineStr"/>
       <c r="BI251" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ251" t="inlineStr"/>
@@ -68799,27 +68799,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>690924</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Braxton Fulford</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-08-25T22:45:00Z</t>
+          <t>2026-08-25T22:40:00Z</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -68829,22 +68829,22 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L252" t="n">
@@ -68866,22 +68866,22 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>22.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q252" t="n">
-        <v>22.8</v>
+        <v>50.8</v>
       </c>
       <c r="R252" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S252" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T252" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U252" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
@@ -68895,7 +68895,7 @@
       </c>
       <c r="X252" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y252" t="inlineStr">
@@ -68937,12 +68937,12 @@
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ252" t="inlineStr">
@@ -68952,119 +68952,119 @@
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.6% barrel, 3.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>85.88</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>98.2974</t>
+          <t>95.4315</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>0.2619</t>
+          <t>0.2684</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.0745</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>0.2256</t>
+          <t>0.2498</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>71.57</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>0.3528</t>
+          <t>0.4688</t>
         </is>
       </c>
       <c r="BE252" t="inlineStr">
         <is>
-          <t>0.1109</t>
+          <t>0.1988</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG252" t="inlineStr"/>
       <c r="BH252" t="inlineStr"/>
       <c r="BI252" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ252" t="inlineStr"/>
@@ -69075,27 +69075,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>623168</t>
+          <t>690924</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Tyler Heineman</t>
+          <t>Braxton Fulford</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-25T22:45:00Z</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -69105,26 +69105,26 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L253" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -69142,22 +69142,22 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q253" t="n">
-        <v>54.7</v>
+        <v>22.8</v>
       </c>
       <c r="R253" t="n">
         <v>28.2</v>
       </c>
       <c r="S253" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T253" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U253" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
@@ -69171,7 +69171,7 @@
       </c>
       <c r="X253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y253" t="inlineStr">
@@ -69213,12 +69213,12 @@
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -69228,119 +69228,119 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.9% barrel, 24.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.6% barrel, 3.1 HR allowed</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>92.5598</t>
+          <t>98.2974</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>0.2755</t>
+          <t>0.2619</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>0.0552</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>0.2527</t>
+          <t>0.2256</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>65.61</t>
+          <t>71.57</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD253" t="inlineStr">
         <is>
-          <t>0.4071</t>
+          <t>0.3528</t>
         </is>
       </c>
       <c r="BE253" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.1109</t>
         </is>
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="BG253" t="inlineStr"/>
       <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ253" t="inlineStr"/>
@@ -69351,27 +69351,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>623168</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Tyler Heineman</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -69386,12 +69386,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -69400,7 +69400,7 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -69414,26 +69414,26 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P254" t="n">
-        <v>10.8</v>
+        <v>0.3</v>
       </c>
       <c r="Q254" t="n">
-        <v>51.7</v>
+        <v>54.7</v>
       </c>
       <c r="R254" t="n">
-        <v>19.3</v>
+        <v>28.2</v>
       </c>
       <c r="S254" t="n">
         <v>40.2</v>
       </c>
       <c r="T254" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U254" t="n">
-        <v>22.9</v>
+        <v>12</v>
       </c>
       <c r="V254" t="inlineStr">
         <is>
@@ -69489,12 +69489,12 @@
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ254" t="inlineStr">
@@ -69504,12 +69504,12 @@
       </c>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 3/15, 0 HR</t>
         </is>
       </c>
       <c r="AL254" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.9% barrel, 24.4 HR allowed</t>
         </is>
       </c>
       <c r="AM254" t="inlineStr">
@@ -69519,104 +69519,104 @@
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>97.2632</t>
+          <t>92.5598</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.2755</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>0.0921</t>
+          <t>0.0552</t>
         </is>
       </c>
       <c r="AT254" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.2527</t>
         </is>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>65.61</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD254" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE254" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BG254" t="inlineStr"/>
       <c r="BH254" t="inlineStr"/>
       <c r="BI254" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ254" t="inlineStr"/>
@@ -69627,27 +69627,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -69657,17 +69657,17 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -69676,7 +69676,7 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -69694,22 +69694,22 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>16.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q255" t="n">
-        <v>27.9</v>
+        <v>51.7</v>
       </c>
       <c r="R255" t="n">
-        <v>22.1</v>
+        <v>19.3</v>
       </c>
       <c r="S255" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T255" t="n">
         <v>50</v>
       </c>
       <c r="U255" t="n">
-        <v>36</v>
+        <v>22.9</v>
       </c>
       <c r="V255" t="inlineStr">
         <is>
@@ -69723,7 +69723,7 @@
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -69765,27 +69765,27 @@
       </c>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL255" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
@@ -69795,104 +69795,104 @@
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>98.6634</t>
+          <t>97.2632</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
         <is>
-          <t>0.3372</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>0.0916</t>
+          <t>0.0921</t>
         </is>
       </c>
       <c r="AT255" t="inlineStr">
         <is>
-          <t>0.2958</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>87.84</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD255" t="inlineStr">
         <is>
-          <t>0.4084</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE255" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG255" t="inlineStr"/>
       <c r="BH255" t="inlineStr"/>
       <c r="BI255" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ255" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-25_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25_full.xlsx
@@ -3459,27 +3459,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>677951</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Bobby Witt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:07:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3522,26 +3522,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="R12" t="n">
-        <v>25.4</v>
+        <v>30.4</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>87</v>
+        <v>79.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3597,134 +3597,134 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>92.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.9454</t>
+          <t>103.6387</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.5087</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2327</t>
+          <t>0.2094</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3227</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.99</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2209</t>
+          <t>0.1822</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.4477</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.2006</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3735,27 +3735,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>695491</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Joshua Baez</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3798,26 +3798,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>89.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>27.9</v>
+        <v>48</v>
       </c>
       <c r="R13" t="n">
-        <v>22.1</v>
+        <v>25.4</v>
       </c>
       <c r="S13" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>18.3</v>
+        <v>87</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3873,134 +3873,134 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 1 HR</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.6094</t>
+          <t>100.9454</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.2327</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3227</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>74.99</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>52.11</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.2209</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.84</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4084</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677951</t>
+          <t>695491</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Joshua Baez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25T23:07:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4074,26 +4074,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>56.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>48.1</v>
+        <v>27.9</v>
       </c>
       <c r="R14" t="n">
-        <v>30.4</v>
+        <v>22.1</v>
       </c>
       <c r="S14" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>74.2</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4149,134 +4149,134 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/22, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>92.74</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.6387</t>
+          <t>103.6094</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.5087</t>
+          <t>0.534</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2094</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1822</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.84</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.4084</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.2006</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -15459,27 +15459,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Ronald Acuna</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-25T23:15:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15489,17 +15489,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15522,26 +15522,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>56</v>
+        <v>57.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>27.9</v>
+        <v>33.9</v>
       </c>
       <c r="R56" t="n">
-        <v>22.1</v>
+        <v>30.9</v>
       </c>
       <c r="S56" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T56" t="n">
         <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>83.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15597,134 +15597,134 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/28, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>92.37</t>
+          <t>90.88</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>104.526</t>
+          <t>102.8197</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4512</t>
+          <t>0.4895</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.2349</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3326</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>62.81</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>36.37</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1799</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>87.84</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.4084</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.1371</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr"/>
       <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -15735,27 +15735,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-25T23:15:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15765,17 +15765,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -15798,26 +15798,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>57.7</v>
+        <v>44.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>33.9</v>
+        <v>39.2</v>
       </c>
       <c r="R57" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="S57" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T57" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -15873,27 +15873,27 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 6.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -15903,104 +15903,104 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>42.93</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.88</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>102.8197</t>
+          <t>100.8399</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4895</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.2349</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.1371</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr"/>
       <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16011,27 +16011,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>676475</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16041,17 +16041,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16074,26 +16074,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>44.1</v>
+        <v>53.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>39.2</v>
+        <v>27.9</v>
       </c>
       <c r="R58" t="n">
-        <v>28.2</v>
+        <v>22.1</v>
       </c>
       <c r="S58" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T58" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>66.7</v>
+        <v>36</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16179,104 +16179,104 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>91.84</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>100.8399</t>
+          <t>102.0399</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.5158</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2263</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.3716</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>73.21</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1886</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.84</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.4084</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16287,12 +16287,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>676475</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -16350,11 +16350,11 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>53.6</v>
+        <v>56</v>
       </c>
       <c r="Q59" t="n">
         <v>27.9</v>
@@ -16363,13 +16363,13 @@
         <v>22.1</v>
       </c>
       <c r="S59" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T59" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U59" t="n">
-        <v>36</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16425,97 +16425,97 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>91.84</t>
+          <t>92.37</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>102.0399</t>
+          <t>104.526</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.5158</t>
+          <t>0.4512</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.2263</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.3716</t>
+          <t>0.3326</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>83.05</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.1886</t>
+          <t>0.1799</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -32089,7 +32089,7 @@
         <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
@@ -32160,7 +32160,7 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 11/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
@@ -46971,27 +46971,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-25T22:45:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -47001,14 +47001,26 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Walbert Ureña</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>700712</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L172" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -47022,26 +47034,26 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P172" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Q172" t="n">
         <v>16</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>40.2</v>
       </c>
       <c r="R172" t="n">
         <v>28.2</v>
       </c>
       <c r="S172" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T172" t="n">
         <v>75</v>
       </c>
       <c r="U172" t="n">
-        <v>56.6</v>
+        <v>23.4</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
@@ -47055,7 +47067,7 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
@@ -47080,7 +47092,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr"/>
@@ -47097,27 +47109,27 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -47127,80 +47139,104 @@
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>40.36</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>97.6261</t>
+          <t>99.6641</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3608</t>
+          <t>0.4278</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.1073</t>
+          <t>0.1466</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>67.29</t>
+          <t>70.34</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="BA172" t="inlineStr"/>
-      <c r="BB172" t="inlineStr"/>
-      <c r="BC172" t="inlineStr"/>
-      <c r="BD172" t="inlineStr"/>
-      <c r="BE172" t="inlineStr"/>
-      <c r="BF172" t="inlineStr"/>
+          <t>0.1633</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>0.301</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
       <c r="BG172" t="inlineStr"/>
       <c r="BH172" t="inlineStr"/>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -47211,27 +47247,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-25T22:40:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -47241,26 +47277,14 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Walbert Ureña</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>700712</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -47274,26 +47298,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>29.7</v>
+        <v>25.4</v>
       </c>
       <c r="Q173" t="n">
-        <v>16</v>
+        <v>40.2</v>
       </c>
       <c r="R173" t="n">
-        <v>28.2</v>
+        <v>21.5</v>
       </c>
       <c r="S173" t="n">
-        <v>92.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="T173" t="n">
         <v>75</v>
       </c>
       <c r="U173" t="n">
-        <v>23.4</v>
+        <v>100</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -47307,7 +47331,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -47332,7 +47356,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47354,22 +47378,22 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -47379,104 +47403,80 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>99.6641</t>
+          <t>98.5793</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.4278</t>
+          <t>0.3628</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1466</t>
+          <t>0.1335</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.3441</t>
+          <t>0.3046</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>70.34</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>40.52</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1633</t>
-        </is>
-      </c>
-      <c r="BA173" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="BB173" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="BC173" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
-      </c>
-      <c r="BD173" t="inlineStr">
-        <is>
-          <t>0.301</t>
-        </is>
-      </c>
-      <c r="BE173" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="BF173" t="inlineStr">
-        <is>
-          <t>23.1</t>
-        </is>
-      </c>
+          <t>0.1279</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr"/>
+      <c r="BB173" t="inlineStr"/>
+      <c r="BC173" t="inlineStr"/>
+      <c r="BD173" t="inlineStr"/>
+      <c r="BE173" t="inlineStr"/>
+      <c r="BF173" t="inlineStr"/>
       <c r="BG173" t="inlineStr"/>
       <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47487,27 +47487,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>681508</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Mickey Gasper</t>
+          <t>LaMonte Wade</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-25T22:40:00Z</t>
+          <t>2026-08-25T23:05:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47517,12 +47517,24 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>701542</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L174" t="n">
         <v>38.6</v>
       </c>
@@ -47538,26 +47550,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>25.4</v>
+        <v>14.5</v>
       </c>
       <c r="Q174" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="R174" t="n">
-        <v>21.5</v>
+        <v>38.2</v>
       </c>
       <c r="S174" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T174" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U174" t="n">
-        <v>100</v>
+        <v>8.5</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47571,7 +47583,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -47596,7 +47608,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -47613,27 +47625,27 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -47643,80 +47655,104 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>98.5793</t>
+          <t>98.3018</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3628</t>
+          <t>0.2993</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1335</t>
+          <t>0.0999</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.3046</t>
+          <t>0.2831</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1279</t>
-        </is>
-      </c>
-      <c r="BA174" t="inlineStr"/>
-      <c r="BB174" t="inlineStr"/>
-      <c r="BC174" t="inlineStr"/>
-      <c r="BD174" t="inlineStr"/>
-      <c r="BE174" t="inlineStr"/>
-      <c r="BF174" t="inlineStr"/>
+          <t>0.108</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>8.87</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>90.86</t>
+        </is>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>0.4267</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>0.1659</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>24.03</t>
+        </is>
+      </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -47727,27 +47763,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>LaMonte Wade</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-25T23:05:00Z</t>
+          <t>2026-08-25T22:40:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -47762,12 +47798,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -47776,7 +47812,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -47794,13 +47830,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>14.5</v>
+        <v>19.7</v>
       </c>
       <c r="Q175" t="n">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="R175" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S175" t="n">
         <v>59.8</v>
@@ -47809,7 +47845,7 @@
         <v>80</v>
       </c>
       <c r="U175" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -47865,12 +47901,12 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -47880,12 +47916,12 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -47895,104 +47931,104 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>98.3018</t>
+          <t>97.8418</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.2993</t>
+          <t>0.3129</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.0999</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.2831</t>
+          <t>0.2652</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.4267</t>
+          <t>0.4688</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1988</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
       <c r="BH175" t="inlineStr"/>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -48003,27 +48039,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-25T22:40:00Z</t>
+          <t>2026-08-25T22:45:00Z</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -48033,24 +48069,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Jackson Jobe</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>695549</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="n">
         <v>38.5</v>
       </c>
@@ -48070,22 +48094,22 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>19.7</v>
+        <v>16</v>
       </c>
       <c r="Q176" t="n">
-        <v>51.1</v>
+        <v>40.2</v>
       </c>
       <c r="R176" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="S176" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T176" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U176" t="n">
-        <v>0.8</v>
+        <v>50.3</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -48099,7 +48123,7 @@
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">
@@ -48124,7 +48148,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr"/>
@@ -48141,27 +48165,27 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -48171,104 +48195,80 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>97.8418</t>
+          <t>97.6261</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>0.3129</t>
+          <t>0.3608</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1073</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2652</t>
+          <t>0.287</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>67.29</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>0.1554</t>
-        </is>
-      </c>
-      <c r="BA176" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="BB176" t="inlineStr">
-        <is>
-          <t>41.34</t>
-        </is>
-      </c>
-      <c r="BC176" t="inlineStr">
-        <is>
-          <t>88.47</t>
-        </is>
-      </c>
-      <c r="BD176" t="inlineStr">
-        <is>
-          <t>0.4688</t>
-        </is>
-      </c>
-      <c r="BE176" t="inlineStr">
-        <is>
-          <t>0.1988</t>
-        </is>
-      </c>
-      <c r="BF176" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
-      </c>
+          <t>0.134</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr"/>
+      <c r="BB176" t="inlineStr"/>
+      <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
       <c r="BG176" t="inlineStr"/>
       <c r="BH176" t="inlineStr"/>
       <c r="BI176" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ176" t="inlineStr"/>
@@ -54075,12 +54075,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -54105,7 +54105,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -54138,11 +54138,11 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0.2</v>
+        <v>12</v>
       </c>
       <c r="Q198" t="n">
         <v>51.1</v>
@@ -54151,13 +54151,13 @@
         <v>27.6</v>
       </c>
       <c r="S198" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T198" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U198" t="n">
-        <v>35.6</v>
+        <v>39.1</v>
       </c>
       <c r="V198" t="inlineStr">
         <is>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
@@ -54213,12 +54213,12 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
@@ -54228,12 +54228,12 @@
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
@@ -54243,67 +54243,67 @@
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>92.869</t>
+          <t>97.4095</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>0.3066</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0998</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>0.2725</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>0.0528</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
@@ -54351,27 +54351,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>699625</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Jimmy Crooks</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-25T22:40:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -54381,17 +54381,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Jackson Jobe</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -54414,26 +54414,26 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>12</v>
+        <v>41.8</v>
       </c>
       <c r="Q199" t="n">
-        <v>51.1</v>
+        <v>27.9</v>
       </c>
       <c r="R199" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S199" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T199" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U199" t="n">
-        <v>39.1</v>
+        <v>5.7</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -54489,12 +54489,12 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
@@ -54504,119 +54504,119 @@
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>97.4095</t>
+          <t>100.5488</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.0998</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.2636</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>71.87</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1538</t>
+          <t>0.1278</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>87.84</t>
         </is>
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>0.4688</t>
+          <t>0.4084</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>0.1988</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -54627,27 +54627,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>699625</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Jimmy Crooks</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-25T22:40:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -54657,17 +54657,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -54676,7 +54676,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -54694,22 +54694,22 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>41.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q200" t="n">
-        <v>27.9</v>
+        <v>51.1</v>
       </c>
       <c r="R200" t="n">
-        <v>22.1</v>
+        <v>27.6</v>
       </c>
       <c r="S200" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T200" t="n">
         <v>80</v>
       </c>
       <c r="U200" t="n">
-        <v>5.7</v>
+        <v>30.2</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -54765,12 +54765,12 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
@@ -54780,119 +54780,119 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>100.5488</t>
+          <t>92.869</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3066</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.2636</t>
+          <t>0.2725</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>71.87</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1278</t>
+          <t>0.0528</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>87.84</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.4084</t>
+          <t>0.4688</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.1988</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr"/>
       <c r="BH200" t="inlineStr"/>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -74849,27 +74849,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>677951</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Bobby Witt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:07:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -74879,17 +74879,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -74912,26 +74912,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="R12" t="n">
-        <v>25.4</v>
+        <v>30.4</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>87</v>
+        <v>79.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -74945,7 +74945,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -74987,134 +74987,134 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>92.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.9454</t>
+          <t>103.6387</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.5087</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2327</t>
+          <t>0.2094</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3227</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.99</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2209</t>
+          <t>0.1822</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.4477</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.2006</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -75125,27 +75125,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>695491</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Joshua Baez</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -75160,12 +75160,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -75174,7 +75174,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -75188,26 +75188,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>89.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>27.9</v>
+        <v>48</v>
       </c>
       <c r="R13" t="n">
-        <v>22.1</v>
+        <v>25.4</v>
       </c>
       <c r="S13" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>18.3</v>
+        <v>87</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -75246,7 +75246,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -75263,134 +75263,134 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 1 HR</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.6094</t>
+          <t>100.9454</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.2327</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3227</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>74.99</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>52.11</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.2209</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.84</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4084</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -75401,27 +75401,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677951</t>
+          <t>695491</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Joshua Baez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25T23:07:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -75431,17 +75431,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -75450,7 +75450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -75464,26 +75464,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>56.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>48.1</v>
+        <v>27.9</v>
       </c>
       <c r="R14" t="n">
-        <v>30.4</v>
+        <v>22.1</v>
       </c>
       <c r="S14" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>74.2</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -75497,7 +75497,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -75522,7 +75522,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -75539,134 +75539,134 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/22, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>92.74</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.6387</t>
+          <t>103.6094</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.5087</t>
+          <t>0.534</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2094</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1822</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.84</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.4084</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.2006</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
